--- a/mapping/STG_DTM/Mapping_STG_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/STG_DTM/Mapping_STG_FCT_RLOS_APPLICATION.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact bảng hồ sơ tín dụng RLOS, ảnh chụp trạng thái cuối ngày, grain 1 dòng/hồ sơ/ngày — bản copy 1:1 từ SB_DWH.FCT_RLOS_APPLICATION sang STG_DTM</t>
+          <t>Bản copy 1:1 từ SB_DWH.FCT_RLOS_APPLICATION tại tầng STG_DTM (vùng chìa, lát cắt theo DAYID)</t>
         </is>
       </c>
       <c r="E2" s="52" t="n"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Chạy dữ liệu FULL hàng ngày</t>
+          <t>Chạy dữ liệu T-1 theo DAYID = v_batch_date</t>
         </is>
       </c>
       <c r="E4" s="52" t="n"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -910,118 +910,118 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>PK (2/2) — Mã hồ sơ tín dụng RLOS</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
           <t>WORKSTEP_DECISION_SK</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới bước xử lý - quyết định gần nhất</t>
-        </is>
-      </c>
-      <c r="D19" s="54" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Khóa bước &amp; quyết định cuối</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION của sự kiện hoàn tất gần nhất — đổi tên từ LAST_WORKSTEP_DECISION_SK</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>A.WORKSTEP_DECISION_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product)</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>A.SUB_PRODUCT_SK</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới công ty/tổ chức</t>
+          <t>Mã bước xử lý cuối</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_COMPANY</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t>A.WORKSTEP_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_SK</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới loại thay đổi điều kiện phê duyệt</t>
+          <t>Mã quyết định cuối</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CHANGE_TYPE</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_SK</t>
+          <t>A.DECISION_CODE</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>CARD_PROMOTION_SK</t>
+          <t>SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1031,24 +1031,24 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khuyến mãi thẻ</t>
+          <t>Khóa sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION</t>
+          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product)</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>A.CARD_PROMOTION_SK</t>
+          <t>A.SUB_PRODUCT_SK</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1058,204 +1058,393 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — Mã hồ sơ tín dụng RLOS</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
+          <t>A.SUB_PRODUCT_CODE</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>PROCESSED_DATE</t>
+          <t>COMPANY_SK</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Ngày xử lý</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên</t>
+          <t>Khóa tới DIM_LOS_COMPANY</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.PROCESSED_DATE</t>
+          <t>A.COMPANY_SK</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>CREATION_DATE</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Ngày tạo hồ sơ</t>
+          <t>Mã đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Ngày khởi tạo hồ sơ</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.CREATION_DATE</t>
+          <t>A.COMPANY_CODE</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_AMT_FINAL</t>
+          <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(25,2)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
+          <t>Khóa loại thay đổi</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
+          <t>Khóa tới DIM_RLOS_CHANGE_TYPE</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.APPROVED_AMT_FINAL</t>
+          <t>A.CHANGE_TYPE_SK</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_TERM</t>
+          <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(15)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Mã loại thay đổi</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.APPROVED_TERM</t>
+          <t>A.CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>CURRENCY_CODE</t>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Loại tiền</t>
+          <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Loại tiền (BC3.CURRENCY)</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.CURRENCY_CODE</t>
+          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_REQUEST</t>
+          <t>CARD_PROMOTION_SK</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
+          <t>Khóa ưu đãi phí thẻ</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_REQUEST</t>
+          <t>A.CARD_PROMOTION_SK</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
+          <t>PROMOTION_CODE</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Mã ưu đãi phí</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>A.PROMOTION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>PROCESSED_DATE</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>A.PROCESSED_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Ngày khởi tạo hồ sơ</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Ngày khởi tạo hồ sơ</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>A.CREATION_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(25,2)</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối cùng</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(15)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>CURRENCY_CODE</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Loại tiền (BC3.CURRENCY)</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>A.CURRENCY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_REQUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên giá trị thô</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
         </is>

--- a/mapping/STG_DTM/Mapping_STG_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/STG_DTM/Mapping_STG_FCT_RLOS_APPLICATION.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bản copy 1:1 từ SB_DWH.FCT_RLOS_APPLICATION tại tầng STG_DTM (vùng chìa, lát cắt theo DAYID)</t>
+          <t>Bảng FACT hồ sơ tín dụng RLOS (bán lẻ/cá nhân) — ảnh trạng thái cuối ngày, số tiền/kỳ hạn phê duyệt cuối cùng. Bản sao 1:1 tại STG_DTM, cắt lát đúng 1 ngày ETL.</t>
         </is>
       </c>
       <c r="E2" s="52" t="n"/>
@@ -856,7 +856,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -874,7 +874,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: FCT_RLOS_APPLICATION (SB_DWH). Ngày dữ liệu, dạng số YYYYMMDD</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD — Driving: FCT_RLOS_APPLICATION (SB_DWH). Cắt lát Fact: chỉ lấy đúng 1 ngày = ngày ETL chạy (v_batch_date). Điều kiện lọc này áp dụng chung cho toàn bộ bảng.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — Mã hồ sơ tín dụng RLOS</t>
+          <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>SUB_PRODUCT_CODE</t>
+          <t>PRODUCTLINE_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1058,132 +1058,132 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã sản phẩm nhánh</t>
+          <t>Mã dòng sản phẩm</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
+          <t>CỘT MỚI (review 2026-10-27) — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.SUB_PRODUCT_CODE</t>
+          <t>A.PRODUCTLINE_CODE</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_SK</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Khóa đơn vị kinh doanh</t>
+          <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_COMPANY</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_SK</t>
+          <t>A.SUB_PRODUCT_CODE</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_CODE</t>
+          <t>COMPANY_SK</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Mã đơn vị kinh doanh</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
+          <t>Khóa tới DIM_LOS_COMPANY</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_CODE</t>
+          <t>A.COMPANY_SK</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_SK</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Khóa loại thay đổi</t>
+          <t>Mã đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CHANGE_TYPE</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_SK</t>
+          <t>A.COMPANY_CODE</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_CODE</t>
+          <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Mã loại thay đổi</t>
+          <t>Khóa loại thay đổi</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
+          <t>Khóa tới DIM_RLOS_CHANGE_TYPE</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_CODE</t>
+          <t>A.CHANGE_TYPE_SK</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>DETAIL_CHANGE_TYPE_CODE</t>
+          <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Mã chi tiết loại thay đổi</t>
+          <t>Mã loại thay đổi</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
@@ -1203,95 +1203,95 @@
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
+          <t>A.CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>CARD_PROMOTION_SK</t>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Khóa ưu đãi phí thẻ</t>
+          <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.CARD_PROMOTION_SK</t>
+          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>PROMOTION_CODE</t>
+          <t>CARD_PROMOTION_SK</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Mã ưu đãi phí</t>
+          <t>Khóa ưu đãi phí thẻ</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>A.PROMOTION_CODE</t>
+          <t>A.CARD_PROMOTION_SK</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>PROCESSED_DATE</t>
+          <t>PROMOTION_CODE</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Ngày xử lý hồ sơ</t>
+          <t>Mã ưu đãi phí</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên</t>
+          <t>CỘT MỚI — BK cạnh SK, bê 1:1 từ SB_DWH</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>A.PROCESSED_DATE</t>
+          <t>A.PROMOTION_CODE</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>CREATION_DATE</t>
+          <t>PROCESSED_DATE</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
@@ -1301,150 +1301,177 @@
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Ngày khởi tạo hồ sơ</t>
+          <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
       <c r="D33" s="54" t="inlineStr">
         <is>
-          <t>Ngày khởi tạo hồ sơ</t>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên</t>
         </is>
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
-          <t>A.CREATION_DATE</t>
+          <t>A.PROCESSED_DATE</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_AMT_FINAL</t>
+          <t>CREATION_DATE</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(25,2)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối</t>
+          <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
       <c r="D34" s="54" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
+          <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
       <c r="E34" s="31" t="inlineStr">
         <is>
-          <t>A.APPROVED_AMT_FINAL</t>
+          <t>A.CREATION_DATE</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_TERM</t>
+          <t>APPROVED_AMT_FINAL</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(15)</t>
+          <t>NUMBER(25,2)</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Hạn mức phê duyệt cuối</t>
         </is>
       </c>
       <c r="D35" s="54" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Hạn mức phê duyệt cuối cùng</t>
         </is>
       </c>
       <c r="E35" s="31" t="inlineStr">
         <is>
-          <t>A.APPROVED_TERM</t>
+          <t>A.APPROVED_AMT_FINAL</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(15)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
           <t>CURRENCY_CODE</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Loại tiền</t>
         </is>
       </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>Loại tiền (BC3.CURRENCY)</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Loại tiền (BC3.CURRENCY). Đồng bộ cột từ SB_DWH (BC3.CURRENCY).</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>A.CURRENCY_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>CHANGE_REQUEST</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
-        </is>
-      </c>
-      <c r="D37" s="54" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>A.CHANGE_REQUEST</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
         <is>
+          <t>CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_REQUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện</t>
         </is>
       </c>
-      <c r="D38" s="54" t="inlineStr">
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên giá trị thô</t>
         </is>
       </c>
-      <c r="E38" s="31" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
         </is>
